--- a/survey_templates/034_makeup_storage_and_hygiene_habit_survey--survey_templates.xlsx
+++ b/survey_templates/034_makeup_storage_and_hygiene_habit_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_am_a_beauty_professional',_'value':_'i_am_a_beauty_professional'}</t>
+          <t>yes,_i_am_a_beauty_professional</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I am a beauty professional', 'value': 'I am a beauty professional'}</t>
+          <t>Yes, I am a beauty professional</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'no,_i_am_not_a_beauty_professional',_'value':_'no,_i_am_not_a_beauty_professional'}</t>
+          <t>no,_i_am_not_a_beauty_professional</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'No, I am not a beauty professional', 'value': 'No, I am not a beauty professional'}</t>
+          <t>No, I am not a beauty professional</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)',_'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)', 'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'16-24',_'value':_'16-24'}</t>
+          <t>16-24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '16-24', 'value': '16-24'}</t>
+          <t>16-24</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'25-34',_'value':_'25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '25-34', 'value': '25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'35-44',_'value':_'35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '35-44', 'value': '35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'45-54',_'value':_'45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '45-54', 'value': '45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'55_or_older',_'value':_'55_or_older'}</t>
+          <t>55_or_older</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '55 or older', 'value': '55 or older'}</t>
+          <t>55 or older</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)',_'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)', 'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'high_school_or_lower',_'value':_'high_school_or_lower'}</t>
+          <t>high_school_or_lower</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'High School or Lower', 'value': 'High School or Lower'}</t>
+          <t>High School or Lower</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_"bachelor's_degree_or_higher",_'value':_"bachelor's_degree_or_higher"}</t>
+          <t>bachelor's_degree_or_higher</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': "Bachelor's degree or Higher", 'value': "Bachelor's degree or Higher"}</t>
+          <t>Bachelor's degree or Higher</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)',_'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)', 'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Email', 'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Phone', 'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)',_'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)', 'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
